--- a/outputs/FNX-20260701-002_74_Grafton_Street.xlsx
+++ b/outputs/FNX-20260701-002_74_Grafton_Street.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consistency Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Takeoff" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Consistency Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Takeoff" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -71,7 +71,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -98,14 +98,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FDF7F2"/>
+        <bgColor rgb="00FDF7F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F2F7FD"/>
         <bgColor rgb="00F2F7FD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDECEF"/>
-        <bgColor rgb="00FDECEF"/>
+        <fgColor rgb="00F2FDF8"/>
+        <bgColor rgb="00F2FDF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -135,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -180,6 +186,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -547,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -595,7 +610,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -605,7 +620,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -616,7 +631,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>69.3%</t>
         </is>
       </c>
     </row>
@@ -659,7 +674,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>2136ALSD</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -669,116 +684,116 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Dimension mismatch for 2136ALSD (Kitchen/Living): Plans 2136H�820W vs NatHERS 2100H�3600W.</t>
+          <t>Dimension mismatch for 1118 (Bedroom 3): Plans 1100H×1800W vs NatHERS 1100H×1810W.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Type Mismatch</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Type mismatch for 1806 (WIR): Plans 'awning' vs NatHERS 'fixed'.</t>
+          <t>Dimension Mismatch</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Dimension mismatch for 1006 (ens): Plans 1000H×600W vs NatHERS 1800H×600W.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1118</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Dimension Mismatch</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for 1118 (Bedroom 3): Plans 1100H�1800W vs NatHERS 1100H�1810W.</t>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Missing in Plans</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1118</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Type Mismatch</t>
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Missing in Plans</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Type mismatch for 1118 (Bedroom 3): Plans 'awning' vs NatHERS 'sliding'.</t>
+          <t>1117 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Low Confidence</t>
+          <t>Missing in Plans</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>1118 (Bedroom 3): Low confidence (65%) � verify specs manually.</t>
+          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1115</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Type Mismatch</t>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Missing in Plans</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Type mismatch for 1115 (BATH): Plans 'awning' vs NatHERS 'sliding'.</t>
+          <t>1818 (Bedroom 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Dimension Mismatch</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for 1006 (ens): Plans 1000H�600W vs NatHERS 1800H�600W.</t>
+          <t>1124</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Missing in Plans</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>1124 (Kitchen/Living) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -788,14 +803,14 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>D1 (LDRY) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -805,58 +820,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>1117 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>1105</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>1818 (Bedroom 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>1124</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>1124 (Kitchen/Living) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>D2 (ENTRY) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
@@ -871,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -880,12 +844,12 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -969,31 +933,31 @@
         </is>
       </c>
       <c r="C3" s="16" t="n">
-        <v>2136</v>
+        <v>2100</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>820</v>
+        <v>3600</v>
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
           <t>sliding</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr"/>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>Aluminium B SG High Solar Gain</t>
-        </is>
-      </c>
-      <c r="H3" s="15" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="I3" s="15" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
+          <t>Aluminium B SG High Solar Gain Low-E</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I3" s="15" t="n">
+        <v>0.58</v>
       </c>
       <c r="J3" s="14" t="inlineStr">
         <is>
@@ -1005,59 +969,59 @@
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>WIR</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>1806</t>
         </is>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="19" t="n">
         <v>1800</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="19" t="n">
         <v>600</v>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr"/>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>Aluminium B SG Clear</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="I4" s="15" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="H4" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K4" s="16" t="n">
+      <c r="K4" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="14" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1076,28 +1040,28 @@
         <v>1100</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>1800</v>
+        <v>1810</v>
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
           <t>sliding</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr"/>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
           <t>Aluminium B SG Clear</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
+      <c r="H5" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>0.7</v>
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
@@ -1109,527 +1073,631 @@
       </c>
       <c r="L5" s="17" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>BATH</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>1115</t>
         </is>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="19" t="n">
         <v>1100</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="19" t="n">
         <v>1500</v>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>sliding</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr"/>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>Aluminium B SG Clear</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="I6" s="15" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="H6" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K6" s="16" t="n">
+      <c r="K6" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="14" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L6" s="17" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>ens</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>1006</t>
         </is>
       </c>
-      <c r="C7" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D7" s="19" t="n">
         <v>600</v>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>awning</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr"/>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>Aluminium A SG Clear</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="H7" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K7" s="16" t="n">
+      <c r="K7" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="14" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L7" s="17" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Kitchen/Living</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>1806</t>
         </is>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="19" t="n">
         <v>1800</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="19" t="n">
         <v>600</v>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>awning</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr"/>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>Aluminium A SG Clear</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="J8" s="14" t="inlineStr">
+      <c r="H8" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K8" s="16" t="n">
+      <c r="K8" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L8" s="14" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L8" s="17" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Kitchen/Living</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>1806</t>
         </is>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="19" t="n">
         <v>1800</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="19" t="n">
         <v>600</v>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>awning</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr"/>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>Aluminium A SG Clear</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="H9" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K9" s="16" t="n">
+      <c r="K9" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="14" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Kitchen/Living</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>1806</t>
         </is>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="19" t="n">
         <v>1800</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="19" t="n">
         <v>600</v>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>awning</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr"/>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>Aluminium A SG Clear</t>
         </is>
       </c>
-      <c r="H10" s="15" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="J10" s="14" t="inlineStr">
+      <c r="H10" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K10" s="16" t="n">
+      <c r="K10" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L10" s="14" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Bedroom 1</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>1105</t>
         </is>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="19" t="n">
         <v>1100</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="19" t="n">
         <v>500</v>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>awning</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr"/>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Aluminium A SG Clear</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="H11" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K11" s="16" t="n">
+      <c r="K11" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L11" s="14" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L11" s="17" t="inlineStr">
+        <is>
+          <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Bedroom 1</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>1117</t>
         </is>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="19" t="n">
         <v>1100</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="19" t="n">
         <v>1700</v>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>double_hung</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr"/>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>Aluminium B SG Clear</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="H12" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K12" s="16" t="n">
+      <c r="K12" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L12" s="14" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Bedroom 1</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>1105</t>
         </is>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="19" t="n">
         <v>1100</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="19" t="n">
         <v>500</v>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>awning</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr"/>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>Aluminium A SG Clear</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="J13" s="14" t="inlineStr">
+      <c r="H13" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K13" s="16" t="n">
+      <c r="K13" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L13" s="14" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L13" s="17" t="inlineStr">
+        <is>
+          <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Bedroom 2</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>1818</t>
         </is>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="19" t="n">
         <v>1800</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="19" t="n">
         <v>1800</v>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>sliding</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr"/>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>Aluminium B SG Clear</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="H14" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K14" s="16" t="n">
+      <c r="K14" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L14" s="14" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Kitchen/Living</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>1124</t>
         </is>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="19" t="n">
         <v>1100</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="19" t="n">
         <v>2400</v>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>sliding</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr"/>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>Aluminium B SG Clear</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="H15" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J15" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K15" s="16" t="n">
+      <c r="K15" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L15" s="14" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L15" s="17" t="inlineStr">
+        <is>
+          <t>NatHERS p.6, p.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>LDRY</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>820</v>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>hinged door</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K16" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>NatHERS p.6, p.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>820</v>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>hinged door</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>

--- a/outputs/FNX-20260701-002_74_Grafton_Street.xlsx
+++ b/outputs/FNX-20260701-002_74_Grafton_Street.xlsx
@@ -71,7 +71,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -86,32 +86,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FEF9E7"/>
+        <bgColor rgb="00FEF9E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FDEDEC"/>
         <bgColor rgb="00FDEDEC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF9E7"/>
-        <bgColor rgb="00FEF9E7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDF7F2"/>
-        <bgColor rgb="00FDF7F2"/>
+        <fgColor rgb="00F2FDF8"/>
+        <bgColor rgb="00F2FDF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F7FD"/>
         <bgColor rgb="00F2F7FD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2FDF8"/>
-        <bgColor rgb="00F2FDF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -141,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,16 +150,16 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -186,15 +180,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -562,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -620,7 +605,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -631,7 +616,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>72.0%</t>
         </is>
       </c>
     </row>
@@ -674,153 +659,136 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1118</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
+          <t>2136ALSD</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Dimension Mismatch</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for 1118 (Bedroom 3): Plans 1100H×1800W vs NatHERS 1100H×1810W.</t>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Dimension mismatch for 2136ALSD (Kitchen/Living): Plans 2130H×3600W vs NatHERS 2100H×3600W.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
+          <t>1118</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Dimension Mismatch</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for 1006 (ens): Plans 1000H×600W vs NatHERS 1800H×600W.</t>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Dimension mismatch for 1118 (Bedroom 3): Plans 1100H×1800W vs NatHERS 1100H×1810W.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>Dimension Mismatch</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Dimension mismatch for 1006 (ens): Plans 1000H×600W vs NatHERS 1800H×600W.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1117</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Missing in Plans</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>1117 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1105</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Missing in Plans</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>1117 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1818</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Missing in Plans</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>1818 (Bedroom 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1124</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Missing in Plans</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>1124 (Kitchen/Living) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>1818 (Bedroom 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+          <t>1124</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Missing in Plans</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>D1 (LDRY) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>D2 (ENTRY) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>1124 (Kitchen/Living) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
@@ -1598,104 +1566,104 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>LDRY</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="16" t="n">
         <v>2100</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="16" t="n">
         <v>820</v>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>hinged door</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="G16" s="20" t="n"/>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr">
+      <c r="I16" s="15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K16" s="22" t="n">
+      <c r="K16" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" s="20" t="inlineStr">
+      <c r="L16" s="14" t="inlineStr">
         <is>
           <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>ENTRY</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="16" t="n">
         <v>2100</v>
       </c>
-      <c r="D17" s="22" t="n">
+      <c r="D17" s="16" t="n">
         <v>820</v>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>hinged door</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G17" s="20" t="n"/>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr">
+      <c r="I17" s="15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J17" s="20" t="inlineStr">
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K17" s="22" t="n">
+      <c r="K17" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L17" s="20" t="inlineStr">
+      <c r="L17" s="14" t="inlineStr">
         <is>
           <t>NatHERS p.6, p.7</t>
         </is>

--- a/outputs/FNX-20260701-002_74_Grafton_Street.xlsx
+++ b/outputs/FNX-20260701-002_74_Grafton_Street.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>74.0%</t>
         </is>
       </c>
     </row>
@@ -667,9 +667,9 @@
           <t>Dimension Mismatch</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for 2136ALSD (Kitchen/Living): Plans 2130H×3600W vs NatHERS 2100H×3600W.</t>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Dimension mismatch for 2136ALSD (Kitchen/Living): Plans 2130H×3600W vs NatHERS 2100H×3600W (Difference: 30mm).</t>
         </is>
       </c>
     </row>
@@ -684,9 +684,9 @@
           <t>Dimension Mismatch</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for 1118 (Bedroom 3): Plans 1100H×1800W vs NatHERS 1100H×1810W.</t>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Dimension mismatch for 1118 (Bedroom 3): Plans 1100H×1800W vs NatHERS 1100H×1810W (Difference: 10mm).</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Dimension mismatch for 1006 (ens): Plans 1000H×600W vs NatHERS 1800H×600W.</t>
+          <t>Dimension mismatch for 1006 (ens): Plans 1000H×600W vs NatHERS 1800H×600W (Difference: 800mm).</t>
         </is>
       </c>
     </row>
@@ -1603,11 +1603,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="J16" s="14" t="inlineStr">
-        <is>
-          <t>Aluminium</t>
-        </is>
-      </c>
+      <c r="J16" s="14" t="n"/>
       <c r="K16" s="16" t="n">
         <v>1</v>
       </c>
@@ -1655,11 +1651,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr">
-        <is>
-          <t>Aluminium</t>
-        </is>
-      </c>
+      <c r="J17" s="14" t="n"/>
       <c r="K17" s="16" t="n">
         <v>1</v>
       </c>

--- a/outputs/FNX-20260701-002_74_Grafton_Street.xlsx
+++ b/outputs/FNX-20260701-002_74_Grafton_Street.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -616,7 +616,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>74.3%</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>2136ALSD</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -669,14 +669,14 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Dimension mismatch for 2136ALSD (Kitchen/Living): Plans 2130H×3600W vs NatHERS 2100H×3600W (Difference: 30mm).</t>
+          <t>Dimension mismatch for 1118 (Bedroom 3): Plans 1100H×1800W vs NatHERS 1100H×1810W (Difference: 10mm).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -684,33 +684,33 @@
           <t>Dimension Mismatch</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for 1118 (Bedroom 3): Plans 1100H×1800W vs NatHERS 1100H×1810W (Difference: 10mm).</t>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Dimension mismatch for 1006 (ens): Plans 1000H×600W vs NatHERS 1800H×600W (Difference: 800mm).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Dimension Mismatch</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for 1006 (ens): Plans 1000H×600W vs NatHERS 1800H×600W (Difference: 800mm).</t>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Missing in Plans</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>1117 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
@@ -737,14 +737,14 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>1117 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -754,14 +754,14 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>1818 (Bedroom 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
@@ -770,23 +770,6 @@
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>1818 (Bedroom 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>1124</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>1124 (Kitchen/Living) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
